--- a/Cardiologie/Excel/cardio_12.xlsx
+++ b/Cardiologie/Excel/cardio_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Cardiologie\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0DBF8A-389E-4D35-B675-B59FC1B31167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{865B5F6B-9B46-4F1E-99CA-823D8AA90AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="520">
   <si>
     <t>La maladie athérothrombotique est responsable de plus de 90% des artériopathies.</t>
   </si>
@@ -809,6 +809,777 @@
   </si>
   <si>
     <t>image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document indique que la maladie athérothrombotique est responsable de plus de 90% des cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles peuvent également toucher les membres supérieurs, l'aorte ou les vaisseaux encéphaliques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte énumère toutes ces causes comme des origines emboligènes possibles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le point de départ est une thrombose veineuse profonde des membres inférieurs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle se définit par le passage d'un embole via un foramen ovale perméable </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document précise explicitement que l'aorte et les vaisseaux encéphaliques peuvent être atteints </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces emboles sont effectivement liés au syndrome du défilé thoraco-brachial </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette pathologie survient habituellement chez un sujet jeune à l'effort </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le remplissage progressif des kystes par du mucus finit par obstruer la lumière artérielle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles touchent préférentiellement les artères rénales, les carotides et les artères iliaques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est au contraire une pathologie spécifique du sportif, notamment du cycliste de haut niveau </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle apparaît après un intervalle libre de plusieurs années faisant suite à l'irradiation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document mentionne l'ergot de seigle et certains médicaments comme causes toxiques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte indique au contraire une prédominance féminine </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leur point de départ est une thrombose veineuse profonde située aux membres inférieurs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document confirme que ces trois localisations sont les sièges préférentiels </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est au contraire une pathologie spécifique du sportif de haut niveau </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte confirme que 10 % des artériopathies ont une autre cause que l'athérome </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles peuvent également concerner les membres supérieurs, l'aorte ou l'encéphale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette pathologie est classée parmi les artériopathies non athéromateuses </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle se manifeste par une claudication à l'effort chez des jeunes sans risque d'athérome </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est responsable d'une ischémie d'aval au niveau de l'artère poplitée ou fémorale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La pathologie affecte au contraire préférentiellement la femme (8 femmes pour 1 homme) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'atteinte des artères rénales est effectivement une cause d'hypertension réno-vasculaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte la décrit comme une pathologie spécifique du sportif de haut niveau </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La claudication est décrite comme étant au contraire souvent haute </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles concernent principalement l'aorte avec des extensions périphériques possibles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document confirme la présence de dérivés de l'ergot dans ces médicaments </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette maladie touche essentiellement l'homme jeune de moins de 40 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle fait partie de la triade clinique fréquente associée à cette pathologie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle survient au contraire quasi exclusivement chez la personne âgée de plus de 60 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document présente effectivement ces deux termes comme synonymes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La pathologie affecte au contraire principalement la femme jeune </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte confirme que l'artérite touche les artères de gros et moyen calibre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La maladie est au contraire plus fréquente en Orient et dans le bassin méditerranéen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces ulcérations récidivantes sont effectivement caractéristiques de la maladie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La vascularite peut toucher à la fois les vaisseaux artériels et veineux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle peut effectivement provoquer une claudication fluctuante chez les sujets jeunes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles touchent préférentiellement les artères rénales, les carotides et les iliaques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document la définit au contraire comme une pathologie héréditaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles se divisent en trois types : gros vaisseaux, moyen calibre et petit calibre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte confirme que cette pathologie touche essentiellement l'homme jeune fumeur </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La pathologie présente au contraire plusieurs types d'atteintes cutanées (folliculite, érythème) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils sont effectivement cités comme une cause emboligène possible </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le syndrome est associé à des emboles situés au niveau des membres supérieurs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La claudication apparaît au contraire uniquement lors de l'effort </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'artère poplitée est l'un des deux sièges principaux de la maladie kystique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles se développent spécifiquement au sein d'un territoire ayant été irradié </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'ergot de seigle provoque une vasoconstriction périphérique et non centrale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces trois localisations sont les principales zones touchées par cette pathologie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte lie la maladie à une triade incluant claudication, Raynaud et thrombophlébites </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'aorte et les artères sous-clavières sont les zones préférentiellement atteintes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une atteinte oculaire de type iritis ou uvéite est effectivement décrite </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document confirme que ces artères sont les cibles préférentielles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'ingestion d'ergot de seigle, un champignon parasite, est la cause citée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte mentionne une prédominance féminine avec une prévalence faible </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles peuvent toucher les vaisseaux de gros, de moyen ou de petit calibre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document indique au contraire que la maladie est plus fréquente chez la femme </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces ulcérations récurrentes sont effectivement nécessaires au diagnostic </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document la définit au contraire comme une maladie oblitérante inflammatoire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La prévalence est effectivement accrue chez les Asiatiques et en Europe Centrale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle touche les branches de la carotide externe mais également l’artère ophtalmique (branche de l'interne) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La fièvre est citée parmi les symptômes cliniques du sujet âgé </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle survient quasi exclusivement chez la personne âgée de plus de 60 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement repose sur la corticothérapie car les AINS sont jugés insuffisants </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les artères sous-clavières sont au contraire préférentiellement atteintes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La pathologie est au contraire décrite comme étant plus sévère chez les hommes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le début habituel se situe entre 18 et 40 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le diagnostic repose essentiellement sur la clinique ; aucun critère biologique n'est d'appoint </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La corticothérapie est utilisée pour les formes graves </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils sont indiqués spécifiquement en cas de thrombose veineuse profonde (TVP) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle touche les artères distales mais également les veines </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la maladie de Horton qui est fréquemment associée à la PPR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle touche au contraire surtout la femme jeune </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les pouls périphériques peuvent être abolis (maladie des femmes sans pouls) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La maladie est plus fréquente en Orient et dans les pays du pourtour méditerranéen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les lésions cutanées (folliculite, érythème noueux, etc.) font partie des critères de diagnostic </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le phénomène de Raynaud fait partie de la triade clinique fréquente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte précise que les pouls peuvent être abolis </t>
+  </si>
+  <si>
+    <t xml:space="preserve">On note une incidence élevée des Ag HLA-B5 et HLA-A9 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'atteinte oculaire (iritis, uvéite, névrite) est au contraire un signe possible </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La présence d'aphtes buccaux ou génitaux est nécessaire au diagnostic </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le syndrome est dû à la compression de l'artère poplitée (et non de la veine) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La compression est intermittente et liée à certains mouvements (extension/dorsiflexion) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle survient habituellement chez un sujet jeune sans facteurs de risque d'athérosclérose </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle provoque une insuffisance artérielle lors de l'extension de la jambe et la dorsiflexion du pied </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le diagnostic repose sur la disparition des pouls lors de la dorsiflexion du pied </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'artériographie statique et dynamique permet de visualiser la compression lors des mouvements </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document mentionne l'utilisation de l'artériographie statique et dynamique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le diagnostic de premier choix est l'examen clinique, l'échographie n'est pas citée pour ce syndrome </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La RMN permet de visualiser les anomalies d’insertion musculo-tendineuses </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle touche l'artère poplitée ou l'artère fémorale superficielle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la définition même de la pathogénie de cette maladie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est responsable d'une ischémie d'aval au membre inférieur (poplitée/fémorale) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La claudication est au contraire fluctuante car liée au remplissage/vidange des kystes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le mucus remplit les kystes qui obstruent progressivement la lumière artérielle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les kystes se vident habituellement dans la lumière artérielle (et non veineuse) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lorsque les kystes se vident, le flux redevient normal et la claudication disparaît </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le diagnostic repose effectivement sur ces différents examens </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle affecte préférentiellement la femme avec un rapport de 8 femmes pour 1 homme </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle peut s'accompagner ou non de fibrose de la limitante élastique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'aspect en "collier de perles" est caractéristique de la forme touchant la média </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle peut toucher l'intima, la média ou l'adventice </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La forme la plus fréquente touche effectivement la média (hyperplasie) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'atteinte des artères rénales est une cause d'HTA réno-vasculaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces trois complications sont possibles lors d'une atteinte carotidienne </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est une pathologie spécifique du sportif, en particulier du cycliste de haut niveau </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les sténoses sont liées à des frottements répétés dans la région iliaque </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les sténoses siègent au niveau de l'artère iliaque externe dans 90% des cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il s'agit de lésions intimales fibreuses et pauci-cellulaires (peu de cellules) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les lésions fibreuses de l'intima vont oblitérer progressivement l'artère </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La claudication survient pour un effort important (ischémie d'effort) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La clinique est effectivement similaire à celle de l'AOMI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La chirurgie est au contraire souvent difficile ; on préfère le traitement endovasculaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement de préférence est conservateur ou endovasculaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle survient après un intervalle libre de plusieurs années </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toutes les artères sont effectivement susceptibles de subir un traumatisme </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traumatisme le plus fréquent est la rupture de l'aorte thoracique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document cite la rupture de l'aorte thoracique, pas de la valve aortique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document confirme cette statistique pour les accidents sur la voie publique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La rupture de l'aorte thoracique peut effectivement être liée à des chutes de grande hauteur ou défenestrations </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il s'agit au contraire d'une déchirure le plus souvent circonférentielle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La déchirure circonférentielle de l'intima conduit bien à la formation d'une vraie et d'une fausse lumière </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les dissections peuvent s'étendre aux artères des membres inférieurs et donner des symptômes périphériques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est le 3ème trimestre de la grossesse qui est cité comme facteur prédisposant </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’HTA est effectivement un facteur prédisposant dans 70% des cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement dépend du type de dissection (A ou B) et du mode de présentation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tous ces facteurs sont listés comme prédisposant aux dissections artérielles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certains toxiques (comme l'ergot de seigle) peuvent effectivement occasionner un vasospasme artériel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'ergot de seigle est décrit comme un champignon parasite des céréales </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il contient divers alcaloïdes dérivés de l’acide lysergique (pas arachidonique) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'utilisation de certains médicaments anti-migraineux expose au risque d'ergotisme </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'ergotisme se manifeste par des spasmes artériels périphériques fluctuants avec ischémie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est caractérisée par une calcification et une fragmentation (pas un allongement) des fibres </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La prévalence est effectivement estimée entre 1/25.000 et 1/100.000 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document précise au contraire que cette pathologie n'évolue jamais vers l’amputation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les calcifications artérielles induisent effectivement une artériosclérose précoce </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle se manifeste par une claudication, des papules jaunâtres (pas rougeâtres) et un aspect de peau d'orange </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'atteinte oculaire peut au contraire conduire à la cécité </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les hémorragies digestives surviennent dans 5 % des cas (pas 50 %) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le fond d'œil montre effectivement des stries angioïdes divergeant à partir de la papille </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les stries angioïdes correspondent à des craquelures de la membrane de Bruch avec néovaisseaux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte indique explicitement "PAS d’aspirine" en raison du risque d’hémorragies digestives </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'altération des fibres élastiques entraîne au contraire une multitude de complications hémorragiques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle touche les artères distales de petit et moyen calibre (1 à 3 mm) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle constitue effectivement 0,5 à 5 % des artériopathies des membres inférieurs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La maladie touche les artères distales mais également les veines </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il existe au contraire un lien clair entre la pathologie et le tabagisme </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La maladie est liée au tabagisme et probablement à la consommation de cannabis </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La triade associe claudication, phénomène de Raynaud et thrombophlébites superficielles (pas profondes) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La maladie est décrite comme ayant une évolution par poussées </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’artériographie met effectivement en évidence des collatérales spiralées « en tire-bouchon » </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le test d’Allen est cité comme faisant partie du diagnostic clinique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La biologie ne montre rien de spécifique pour la maladie de Buerger </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La biopsie est effectivement rarement possible, sauf en cas de thrombose veineuse superficielle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'examen histologique montre une panvascularite avec thrombus hypercellulaire et cellules multinucléées </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’arrêt du tabac est l'un des éléments clés du traitement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document ne mentionne pas les bêta-bloquants, mais cite les antagonistes calciques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement inclut effectivement ces quatre classes de médicaments </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte précise au contraire que la chirurgie de revascularisation est rarement possible </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La sympathectomie est mentionnée comme ayant des indications très limitées </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Des amputations limitées sont effectivement parfois nécessaires </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'artérite à cellules géantes prédomine au niveau de la média (et non de l'intima) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'atteinte vasculaire est de topographie segmentaire et plurifocale (et non unifocale) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle touche avec prédilection l’aorte et ses branches de division principales </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle touche préférentiellement les branches de la carotide externe (dont la temporale) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La PPR associée se manifeste par des douleurs et raideurs des ceintures scapulaire et pelvienne </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La prévalence est de 9-18 cas pour 100 000 habitants de plus de 50 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les céphalées sont présentes dans 65-70 % des cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La maladie de Horton est effectivement fréquemment associée à une PPR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle touche l'aorte et les artères de gros et moyen calibre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle touche les artères de petit et moyen calibre (1 à 3 mm) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est effectivement plus fréquente chez la femme </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La prévalence est accrue dans les populations blanches d'Europe et d'Amérique du Nord </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La maladie de Horton survient quasi exclusivement chez la personne âgée de plus de 60 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces trois facteurs sont suspectés de jouer un rôle dans l'étiologie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les artères temporales sont effectivement décrites comme douloureuses à la palpation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle s'accompagne d'une altération de l'état général </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La PPR se manifeste par une douleur et raideur des ceintures scapulaire et pelvienne </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces signes évocateurs sont effectivement présents dans 30-40 % des cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La claudication massétérine est l'un des signes évocateurs de la maladie chez le sujet âgé </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La VS est au contraire décrite comme étant souvent &gt; 50 mm/h </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La biologie montre une anémie et une VS/CRP élevée, mais une augmentation des plaquettes (thrombocytose) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La maladie de Horton s'accompagne effectivement fréquemment d'une cholestase biologique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La VS est effectivement souvent supérieure à 50 mm/h </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’échographie Doppler des artères temporales fait partie des examens de diagnostic cités </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La biopsie montre des cellules polymorphes (et non monomorphes) et géantes dans la média </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document précise explicitement que les AINS sont insuffisants pour traiter l'inflammation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le PET-Scan est cité comme le meilleur choix pour approcher le diagnostic de Takayasu, pas Horton </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement nécessite une corticothérapie d'entretien pendant 1 à 2 ans (pas courte) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La dose de prednisone en phase aiguë est effectivement de 0,5 à 1 mg/kg/j pendant 3 à 6 semaines </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La supplémentation en Calcium et vitamine D est nécessaire lors de la corticothérapie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un traitement d'entretien de 5 à 10 mg/j pendant 1 à 2 ans est nécessaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce traitement prolongé vise effectivement à minimiser le risque de rechute </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est au contraire appelée "maladie des femmes sans pouls" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tous les gros vaisseaux peuvent effectivement être affectés par la maladie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est une artérite inflammatoire et sténosante des artères de gros et moyen calibre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'infiltrat inflammatoire à cellules géantes est à prédominance médio-adventitielle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La crosse de l’aorte et les artères sous-clavières sont préférentiellement atteintes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La pathogénie mentionne au contraire un infiltrat comprenant des cellules géantes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document confirme que la crosse de l'aorte est un siège de prédilection </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle débute effectivement fréquemment à l’adolescence ou avant 20 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La prévalence est de 1 à 2,5 cas par million d'habitants (et non 100 000) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'association à une maladie de Crohn ou une spondylarthrite ankylosante est mentionnée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Des mécanismes immunopathogéniques sont effectivement suspectés </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'infiltrat est composé de cellules mononucléées et géantes, à prédominance médio-adventitielle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La TA est au contraire décrite comme imprenable en cas d'atteinte des sous-clavières </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les symptômes généraux précèdent souvent de plusieurs mois la phase vasculaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'atteinte des artères sous-clavières peut effectivement entraîner l'abolition des pouls </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces symptômes (malaises, fièvre, etc.) précèdent souvent de plusieurs mois les signes vasculaires </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'érythème noueux est un signe cutané cité pour la maladie de Behçet, pas Takayasu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'atteinte des artères rénales peut effectivement provoquer une HTA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document mentionne plusieurs évolutions possibles : fulminante, progressive ou stable </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La biologie est décrite comme étant au contraire aspécifique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le diagnostic biologique montre effectivement une VS augmentée, des Ig augmentées et une anémie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'échographie permet de visualiser l’épaississement des parois artérielles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces deux examens fournissent des renseignements sur la lumière vasculaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le PET Scan est actuellement considéré comme le meilleur choix pour le diagnostic </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte précise au contraire que les biopsies sont rarement possibles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La revascularisation (chirurgicale ou endovasculaire) est parfois nécessaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement comprend effectivement la corticothérapie et les immunosuppresseurs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les immunosuppresseurs sont cités dans le traitement de Behçet et Takayasu, pas Horton </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est associée à des manifestations cutanées, articulaires, nerveuses et vasculaires </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est une vascularite touchant les gros et les petits vaisseaux, artériels ou veineux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le début habituel de la maladie se situe entre 18 et 40 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document mentionne effectivement l'existence de formes familiales </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la maladie de Behçet (et non la TAO) qui nécessite des aphtes pour le diagnostic </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le test pathergique est une hypersensibilité aux points de piqûre, signe de la maladie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les arthrites non déformantes sont présentes chez 25 % des patients </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces trois types d'atteintes cutanées sont cités dans la présentation clinique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'atteinte oculaire peut inclure une névrite optique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle provoque des TVP ou TVS des membres inférieurs dans 25 % des cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La maladie peut entraîner des anévrismes ou des thromboses artérielles, bien que ce soit rare </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est effectivement plus fréquente dans le Bassin Méditerranéen et au Moyen-Orient </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'atteinte digestive (ulcérations) est décrite comme étant peu fréquente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'atteinte du SNC (système nerveux central) fait partie des manifestations diverses </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'érythème noueux est l'une des atteintes cutanées citées </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le critère diagnostique est de plus de 3 ulcérations orales en 12 mois </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle montre une microvascularite dermique dans 60 % des cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les actes invasifs présentent effectivement un risque de formation anévrismale au point de ponction </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La colchicine est au contraire utilisée pour les formes cutanéo-muqueuses </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement est au contraire habituellement conservateur sauf en cas d'ischémie sévère </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La corticothérapie est effectivement indiquée pour le traitement des formes graves </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le méthotrexate est au contraire utilisé pour les formes graves </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’azathioprine est effectivement citée comme traitement des formes graves </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement chirurgical est effectivement impératif en raison du risque de rupture élevé </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte mentionne une hypersensibilité aux points de piqûre (test pathergique) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document précise au contraire que le risque de rupture est élevé </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il s'agit effectivement d'une vascularite touchant les vaisseaux artériels ou veineux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La maladie est plus fréquente dans le Bassin Méditerranéen et au Moyen-Orient </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte cite des atteintes cutanées, oculaires (uvéite), articulaires, nerveuses et vasculaires </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les anévrismes ou thromboses artérielles sont au contraire décrits comme étant rares </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le test est défini comme une hypersensibilité aux points de piqûre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'atteinte digestive se manifeste par des ulcérations de la muqueuse intestinale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement conservateur est effectivement la règle pour les thromboses artérielles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'atteinte artérielle est citée (anévrismes/thromboses) mais sans mention de l'artère pulmonaire </t>
+  </si>
+  <si>
+    <t>Page</t>
   </si>
 </sst>
 </file>
@@ -1156,7 +1927,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G257"/>
+  <dimension ref="A1:H257"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
@@ -1165,7 +1936,7 @@
     <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>256</v>
       </c>
@@ -1179,16 +1950,19 @@
         <v>259</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1198,8 +1972,14 @@
       <c r="C2" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1209,8 +1989,14 @@
       <c r="C3" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1220,8 +2006,14 @@
       <c r="C4" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>265</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1231,8 +2023,14 @@
       <c r="C5" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>266</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1242,8 +2040,14 @@
       <c r="C6" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>267</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1253,8 +2057,14 @@
       <c r="C7" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>268</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1264,8 +2074,14 @@
       <c r="C8" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>269</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1275,8 +2091,14 @@
       <c r="C9" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>270</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1286,8 +2108,14 @@
       <c r="C10" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>271</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1297,8 +2125,14 @@
       <c r="C11" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>272</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1308,8 +2142,14 @@
       <c r="C12" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>273</v>
+      </c>
+      <c r="E12" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1319,8 +2159,14 @@
       <c r="C13" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>274</v>
+      </c>
+      <c r="E13" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1330,8 +2176,14 @@
       <c r="C14" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>275</v>
+      </c>
+      <c r="E14" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1341,8 +2193,14 @@
       <c r="C15" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>276</v>
+      </c>
+      <c r="E15" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1352,8 +2210,14 @@
       <c r="C16" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>277</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1363,8 +2227,14 @@
       <c r="C17" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>278</v>
+      </c>
+      <c r="E17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1374,8 +2244,14 @@
       <c r="C18" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>279</v>
+      </c>
+      <c r="E18" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1385,8 +2261,14 @@
       <c r="C19" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>280</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1396,8 +2278,14 @@
       <c r="C20" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
+        <v>281</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1407,8 +2295,14 @@
       <c r="C21" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>282</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1418,8 +2312,14 @@
       <c r="C22" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>283</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1429,8 +2329,14 @@
       <c r="C23" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>284</v>
+      </c>
+      <c r="E23" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1440,8 +2346,14 @@
       <c r="C24" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>285</v>
+      </c>
+      <c r="E24" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1451,8 +2363,14 @@
       <c r="C25" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>286</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1462,8 +2380,14 @@
       <c r="C26" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
+        <v>287</v>
+      </c>
+      <c r="E26" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1473,8 +2397,14 @@
       <c r="C27" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>288</v>
+      </c>
+      <c r="E27" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1484,8 +2414,14 @@
       <c r="C28" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>289</v>
+      </c>
+      <c r="E28" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1495,8 +2431,14 @@
       <c r="C29" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
+        <v>290</v>
+      </c>
+      <c r="E29" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1506,8 +2448,14 @@
       <c r="C30" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30" t="s">
+        <v>291</v>
+      </c>
+      <c r="E30" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1517,8 +2465,14 @@
       <c r="C31" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>292</v>
+      </c>
+      <c r="E31" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1528,8 +2482,14 @@
       <c r="C32" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>293</v>
+      </c>
+      <c r="E32" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1539,8 +2499,14 @@
       <c r="C33" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>294</v>
+      </c>
+      <c r="E33" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1550,8 +2516,14 @@
       <c r="C34" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
+        <v>295</v>
+      </c>
+      <c r="E34" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1561,8 +2533,14 @@
       <c r="C35" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>296</v>
+      </c>
+      <c r="E35" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -1572,8 +2550,14 @@
       <c r="C36" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36" t="s">
+        <v>297</v>
+      </c>
+      <c r="E36" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1583,8 +2567,14 @@
       <c r="C37" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>298</v>
+      </c>
+      <c r="E37" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1594,8 +2584,14 @@
       <c r="C38" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>299</v>
+      </c>
+      <c r="E38" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1605,8 +2601,14 @@
       <c r="C39" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" t="s">
+        <v>300</v>
+      </c>
+      <c r="E39" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1616,8 +2618,14 @@
       <c r="C40" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
+        <v>301</v>
+      </c>
+      <c r="E40" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -1627,8 +2635,14 @@
       <c r="C41" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41" t="s">
+        <v>302</v>
+      </c>
+      <c r="E41" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -1638,8 +2652,14 @@
       <c r="C42" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" t="s">
+        <v>303</v>
+      </c>
+      <c r="E42" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -1649,8 +2669,14 @@
       <c r="C43" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43" t="s">
+        <v>304</v>
+      </c>
+      <c r="E43" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -1660,8 +2686,14 @@
       <c r="C44" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44" t="s">
+        <v>305</v>
+      </c>
+      <c r="E44" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -1671,8 +2703,14 @@
       <c r="C45" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45" t="s">
+        <v>306</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -1682,8 +2720,14 @@
       <c r="C46" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D46" t="s">
+        <v>307</v>
+      </c>
+      <c r="E46" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -1693,8 +2737,14 @@
       <c r="C47" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47" t="s">
+        <v>308</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -1704,8 +2754,14 @@
       <c r="C48" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D48" t="s">
+        <v>309</v>
+      </c>
+      <c r="E48" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -1715,8 +2771,14 @@
       <c r="C49" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D49" t="s">
+        <v>310</v>
+      </c>
+      <c r="E49" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -1726,8 +2788,14 @@
       <c r="C50" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D50" t="s">
+        <v>311</v>
+      </c>
+      <c r="E50" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -1737,8 +2805,14 @@
       <c r="C51" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D51" t="s">
+        <v>312</v>
+      </c>
+      <c r="E51" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -1748,8 +2822,14 @@
       <c r="C52" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D52" t="s">
+        <v>313</v>
+      </c>
+      <c r="E52" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -1759,8 +2839,14 @@
       <c r="C53" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D53" t="s">
+        <v>314</v>
+      </c>
+      <c r="E53" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -1770,8 +2856,14 @@
       <c r="C54" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D54" t="s">
+        <v>315</v>
+      </c>
+      <c r="E54" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -1781,8 +2873,14 @@
       <c r="C55" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D55" t="s">
+        <v>316</v>
+      </c>
+      <c r="E55" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -1792,8 +2890,14 @@
       <c r="C56" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D56" t="s">
+        <v>317</v>
+      </c>
+      <c r="E56" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -1803,8 +2907,14 @@
       <c r="C57" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D57" t="s">
+        <v>318</v>
+      </c>
+      <c r="E57" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -1814,8 +2924,14 @@
       <c r="C58" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D58" t="s">
+        <v>319</v>
+      </c>
+      <c r="E58" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -1825,8 +2941,14 @@
       <c r="C59" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D59" t="s">
+        <v>320</v>
+      </c>
+      <c r="E59" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -1836,8 +2958,14 @@
       <c r="C60" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D60" t="s">
+        <v>321</v>
+      </c>
+      <c r="E60" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -1847,8 +2975,14 @@
       <c r="C61" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D61" t="s">
+        <v>322</v>
+      </c>
+      <c r="E61" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -1858,8 +2992,14 @@
       <c r="C62" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D62" t="s">
+        <v>323</v>
+      </c>
+      <c r="E62" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -1869,8 +3009,14 @@
       <c r="C63" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D63" t="s">
+        <v>324</v>
+      </c>
+      <c r="E63" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -1880,8 +3026,14 @@
       <c r="C64" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D64" t="s">
+        <v>325</v>
+      </c>
+      <c r="E64" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -1891,8 +3043,14 @@
       <c r="C65" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D65" t="s">
+        <v>326</v>
+      </c>
+      <c r="E65" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -1902,8 +3060,14 @@
       <c r="C66" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D66" t="s">
+        <v>327</v>
+      </c>
+      <c r="E66" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -1913,8 +3077,14 @@
       <c r="C67" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D67" t="s">
+        <v>328</v>
+      </c>
+      <c r="E67" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -1924,8 +3094,14 @@
       <c r="C68" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D68" t="s">
+        <v>329</v>
+      </c>
+      <c r="E68" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -1935,8 +3111,14 @@
       <c r="C69" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D69" t="s">
+        <v>330</v>
+      </c>
+      <c r="E69" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -1946,8 +3128,14 @@
       <c r="C70" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D70" t="s">
+        <v>331</v>
+      </c>
+      <c r="E70" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -1957,8 +3145,14 @@
       <c r="C71" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D71" t="s">
+        <v>332</v>
+      </c>
+      <c r="E71" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -1968,8 +3162,14 @@
       <c r="C72" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D72" t="s">
+        <v>333</v>
+      </c>
+      <c r="E72" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -1979,8 +3179,14 @@
       <c r="C73" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D73" t="s">
+        <v>334</v>
+      </c>
+      <c r="E73" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -1990,8 +3196,14 @@
       <c r="C74" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D74" t="s">
+        <v>335</v>
+      </c>
+      <c r="E74" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -2001,8 +3213,14 @@
       <c r="C75" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D75" t="s">
+        <v>336</v>
+      </c>
+      <c r="E75" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -2012,8 +3230,14 @@
       <c r="C76" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D76" t="s">
+        <v>337</v>
+      </c>
+      <c r="E76" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -2023,8 +3247,14 @@
       <c r="C77" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D77" t="s">
+        <v>338</v>
+      </c>
+      <c r="E77" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -2034,8 +3264,14 @@
       <c r="C78" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D78" t="s">
+        <v>339</v>
+      </c>
+      <c r="E78" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -2045,8 +3281,14 @@
       <c r="C79" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D79" t="s">
+        <v>340</v>
+      </c>
+      <c r="E79" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -2056,8 +3298,14 @@
       <c r="C80" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D80" t="s">
+        <v>341</v>
+      </c>
+      <c r="E80" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -2067,8 +3315,14 @@
       <c r="C81" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D81" t="s">
+        <v>342</v>
+      </c>
+      <c r="E81" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -2078,8 +3332,14 @@
       <c r="C82" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D82" t="s">
+        <v>343</v>
+      </c>
+      <c r="E82" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -2089,8 +3349,14 @@
       <c r="C83" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D83" t="s">
+        <v>344</v>
+      </c>
+      <c r="E83" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -2100,8 +3366,14 @@
       <c r="C84" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D84" t="s">
+        <v>345</v>
+      </c>
+      <c r="E84" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -2111,8 +3383,14 @@
       <c r="C85" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D85" t="s">
+        <v>346</v>
+      </c>
+      <c r="E85" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -2122,8 +3400,14 @@
       <c r="C86" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D86" t="s">
+        <v>347</v>
+      </c>
+      <c r="E86" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -2133,8 +3417,14 @@
       <c r="C87" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D87" t="s">
+        <v>348</v>
+      </c>
+      <c r="E87" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -2144,8 +3434,14 @@
       <c r="C88" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D88" t="s">
+        <v>349</v>
+      </c>
+      <c r="E88" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -2155,8 +3451,14 @@
       <c r="C89" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D89" t="s">
+        <v>350</v>
+      </c>
+      <c r="E89" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -2166,8 +3468,14 @@
       <c r="C90" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D90" t="s">
+        <v>351</v>
+      </c>
+      <c r="E90" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -2177,8 +3485,14 @@
       <c r="C91" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D91" t="s">
+        <v>352</v>
+      </c>
+      <c r="E91" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -2188,8 +3502,14 @@
       <c r="C92" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D92" t="s">
+        <v>353</v>
+      </c>
+      <c r="E92" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -2199,8 +3519,14 @@
       <c r="C93" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D93" t="s">
+        <v>354</v>
+      </c>
+      <c r="E93" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -2210,8 +3536,14 @@
       <c r="C94" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D94" t="s">
+        <v>355</v>
+      </c>
+      <c r="E94" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -2221,8 +3553,14 @@
       <c r="C95" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D95" t="s">
+        <v>356</v>
+      </c>
+      <c r="E95" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -2232,8 +3570,14 @@
       <c r="C96" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D96" t="s">
+        <v>357</v>
+      </c>
+      <c r="E96" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -2243,8 +3587,14 @@
       <c r="C97" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D97" t="s">
+        <v>358</v>
+      </c>
+      <c r="E97" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -2254,8 +3604,14 @@
       <c r="C98" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D98" t="s">
+        <v>359</v>
+      </c>
+      <c r="E98" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -2265,8 +3621,14 @@
       <c r="C99" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D99" t="s">
+        <v>360</v>
+      </c>
+      <c r="E99" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -2276,8 +3638,14 @@
       <c r="C100" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D100" t="s">
+        <v>361</v>
+      </c>
+      <c r="E100" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -2287,8 +3655,14 @@
       <c r="C101" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D101" t="s">
+        <v>362</v>
+      </c>
+      <c r="E101" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -2298,8 +3672,14 @@
       <c r="C102" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D102" t="s">
+        <v>363</v>
+      </c>
+      <c r="E102" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -2309,8 +3689,14 @@
       <c r="C103" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D103" t="s">
+        <v>364</v>
+      </c>
+      <c r="E103" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -2320,8 +3706,14 @@
       <c r="C104" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D104" t="s">
+        <v>365</v>
+      </c>
+      <c r="E104" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -2331,8 +3723,14 @@
       <c r="C105" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D105" t="s">
+        <v>366</v>
+      </c>
+      <c r="E105" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -2342,8 +3740,14 @@
       <c r="C106" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D106" t="s">
+        <v>367</v>
+      </c>
+      <c r="E106" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>106</v>
       </c>
@@ -2353,8 +3757,14 @@
       <c r="C107" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D107" t="s">
+        <v>368</v>
+      </c>
+      <c r="E107" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -2364,8 +3774,14 @@
       <c r="C108" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D108" t="s">
+        <v>369</v>
+      </c>
+      <c r="E108" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>108</v>
       </c>
@@ -2375,8 +3791,14 @@
       <c r="C109" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D109" t="s">
+        <v>370</v>
+      </c>
+      <c r="E109" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -2386,8 +3808,14 @@
       <c r="C110" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D110" t="s">
+        <v>371</v>
+      </c>
+      <c r="E110" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>110</v>
       </c>
@@ -2397,8 +3825,14 @@
       <c r="C111" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D111" t="s">
+        <v>372</v>
+      </c>
+      <c r="E111" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>111</v>
       </c>
@@ -2408,8 +3842,14 @@
       <c r="C112" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D112" t="s">
+        <v>373</v>
+      </c>
+      <c r="E112" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>112</v>
       </c>
@@ -2419,8 +3859,14 @@
       <c r="C113" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D113" t="s">
+        <v>374</v>
+      </c>
+      <c r="E113" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>113</v>
       </c>
@@ -2430,8 +3876,14 @@
       <c r="C114" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D114" t="s">
+        <v>375</v>
+      </c>
+      <c r="E114" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>114</v>
       </c>
@@ -2441,8 +3893,14 @@
       <c r="C115" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D115" t="s">
+        <v>376</v>
+      </c>
+      <c r="E115" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>115</v>
       </c>
@@ -2452,8 +3910,14 @@
       <c r="C116" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D116" t="s">
+        <v>377</v>
+      </c>
+      <c r="E116" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>116</v>
       </c>
@@ -2463,8 +3927,14 @@
       <c r="C117" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D117" t="s">
+        <v>378</v>
+      </c>
+      <c r="E117" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -2474,8 +3944,14 @@
       <c r="C118" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D118" t="s">
+        <v>379</v>
+      </c>
+      <c r="E118" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>118</v>
       </c>
@@ -2485,8 +3961,14 @@
       <c r="C119" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D119" t="s">
+        <v>380</v>
+      </c>
+      <c r="E119" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>119</v>
       </c>
@@ -2496,8 +3978,14 @@
       <c r="C120" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D120" t="s">
+        <v>381</v>
+      </c>
+      <c r="E120" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>120</v>
       </c>
@@ -2507,8 +3995,14 @@
       <c r="C121" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D121" t="s">
+        <v>382</v>
+      </c>
+      <c r="E121" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>121</v>
       </c>
@@ -2518,8 +4012,14 @@
       <c r="C122" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D122" t="s">
+        <v>383</v>
+      </c>
+      <c r="E122" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>122</v>
       </c>
@@ -2529,8 +4029,14 @@
       <c r="C123" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D123" t="s">
+        <v>384</v>
+      </c>
+      <c r="E123" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>123</v>
       </c>
@@ -2540,8 +4046,14 @@
       <c r="C124" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D124" t="s">
+        <v>385</v>
+      </c>
+      <c r="E124" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>124</v>
       </c>
@@ -2551,8 +4063,14 @@
       <c r="C125" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D125" t="s">
+        <v>386</v>
+      </c>
+      <c r="E125" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>125</v>
       </c>
@@ -2562,8 +4080,14 @@
       <c r="C126" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D126" t="s">
+        <v>387</v>
+      </c>
+      <c r="E126" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>126</v>
       </c>
@@ -2573,8 +4097,14 @@
       <c r="C127" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D127" t="s">
+        <v>388</v>
+      </c>
+      <c r="E127" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>127</v>
       </c>
@@ -2584,8 +4114,14 @@
       <c r="C128" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D128" t="s">
+        <v>389</v>
+      </c>
+      <c r="E128" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>128</v>
       </c>
@@ -2595,8 +4131,14 @@
       <c r="C129" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D129" t="s">
+        <v>390</v>
+      </c>
+      <c r="E129" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>129</v>
       </c>
@@ -2606,8 +4148,14 @@
       <c r="C130" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D130" t="s">
+        <v>391</v>
+      </c>
+      <c r="E130" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>130</v>
       </c>
@@ -2617,8 +4165,14 @@
       <c r="C131" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D131" t="s">
+        <v>392</v>
+      </c>
+      <c r="E131" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>131</v>
       </c>
@@ -2628,8 +4182,14 @@
       <c r="C132" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D132" t="s">
+        <v>393</v>
+      </c>
+      <c r="E132" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>132</v>
       </c>
@@ -2639,8 +4199,14 @@
       <c r="C133" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D133" t="s">
+        <v>394</v>
+      </c>
+      <c r="E133" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>133</v>
       </c>
@@ -2650,8 +4216,14 @@
       <c r="C134" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D134" t="s">
+        <v>395</v>
+      </c>
+      <c r="E134" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>134</v>
       </c>
@@ -2661,8 +4233,14 @@
       <c r="C135" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D135" t="s">
+        <v>396</v>
+      </c>
+      <c r="E135" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>135</v>
       </c>
@@ -2672,8 +4250,14 @@
       <c r="C136" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D136" t="s">
+        <v>397</v>
+      </c>
+      <c r="E136" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>136</v>
       </c>
@@ -2683,8 +4267,14 @@
       <c r="C137" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D137" t="s">
+        <v>398</v>
+      </c>
+      <c r="E137" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>137</v>
       </c>
@@ -2694,8 +4284,14 @@
       <c r="C138" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D138" t="s">
+        <v>399</v>
+      </c>
+      <c r="E138" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>138</v>
       </c>
@@ -2705,8 +4301,14 @@
       <c r="C139" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D139" t="s">
+        <v>400</v>
+      </c>
+      <c r="E139" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>139</v>
       </c>
@@ -2716,8 +4318,14 @@
       <c r="C140" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D140" t="s">
+        <v>401</v>
+      </c>
+      <c r="E140" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>140</v>
       </c>
@@ -2727,8 +4335,14 @@
       <c r="C141" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D141" t="s">
+        <v>402</v>
+      </c>
+      <c r="E141" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>141</v>
       </c>
@@ -2738,8 +4352,14 @@
       <c r="C142" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D142" t="s">
+        <v>403</v>
+      </c>
+      <c r="E142" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>142</v>
       </c>
@@ -2749,8 +4369,14 @@
       <c r="C143" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D143" t="s">
+        <v>404</v>
+      </c>
+      <c r="E143" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>143</v>
       </c>
@@ -2760,8 +4386,14 @@
       <c r="C144" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D144" t="s">
+        <v>405</v>
+      </c>
+      <c r="E144" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>144</v>
       </c>
@@ -2771,8 +4403,14 @@
       <c r="C145" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D145" t="s">
+        <v>406</v>
+      </c>
+      <c r="E145" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>145</v>
       </c>
@@ -2782,8 +4420,14 @@
       <c r="C146" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D146" t="s">
+        <v>407</v>
+      </c>
+      <c r="E146" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>146</v>
       </c>
@@ -2793,8 +4437,14 @@
       <c r="C147" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D147" t="s">
+        <v>408</v>
+      </c>
+      <c r="E147" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>147</v>
       </c>
@@ -2804,8 +4454,14 @@
       <c r="C148" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D148" t="s">
+        <v>409</v>
+      </c>
+      <c r="E148" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>148</v>
       </c>
@@ -2815,8 +4471,14 @@
       <c r="C149" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D149" t="s">
+        <v>410</v>
+      </c>
+      <c r="E149" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>149</v>
       </c>
@@ -2826,8 +4488,14 @@
       <c r="C150" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D150" t="s">
+        <v>411</v>
+      </c>
+      <c r="E150" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>150</v>
       </c>
@@ -2837,8 +4505,14 @@
       <c r="C151" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D151" t="s">
+        <v>412</v>
+      </c>
+      <c r="E151" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>151</v>
       </c>
@@ -2848,8 +4522,14 @@
       <c r="C152" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D152" t="s">
+        <v>413</v>
+      </c>
+      <c r="E152" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>152</v>
       </c>
@@ -2859,8 +4539,14 @@
       <c r="C153" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D153" t="s">
+        <v>414</v>
+      </c>
+      <c r="E153" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>153</v>
       </c>
@@ -2870,8 +4556,14 @@
       <c r="C154" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D154" t="s">
+        <v>415</v>
+      </c>
+      <c r="E154" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>154</v>
       </c>
@@ -2881,8 +4573,14 @@
       <c r="C155" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D155" t="s">
+        <v>416</v>
+      </c>
+      <c r="E155" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>155</v>
       </c>
@@ -2892,8 +4590,14 @@
       <c r="C156" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D156" t="s">
+        <v>417</v>
+      </c>
+      <c r="E156" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>156</v>
       </c>
@@ -2903,8 +4607,14 @@
       <c r="C157" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D157" t="s">
+        <v>418</v>
+      </c>
+      <c r="E157" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>157</v>
       </c>
@@ -2914,8 +4624,14 @@
       <c r="C158" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D158" t="s">
+        <v>419</v>
+      </c>
+      <c r="E158" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>158</v>
       </c>
@@ -2925,8 +4641,14 @@
       <c r="C159" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D159" t="s">
+        <v>420</v>
+      </c>
+      <c r="E159" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>159</v>
       </c>
@@ -2936,8 +4658,14 @@
       <c r="C160" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D160" t="s">
+        <v>421</v>
+      </c>
+      <c r="E160" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>160</v>
       </c>
@@ -2947,8 +4675,14 @@
       <c r="C161" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D161" t="s">
+        <v>422</v>
+      </c>
+      <c r="E161" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>161</v>
       </c>
@@ -2958,8 +4692,14 @@
       <c r="C162" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D162" t="s">
+        <v>423</v>
+      </c>
+      <c r="E162" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>162</v>
       </c>
@@ -2969,8 +4709,14 @@
       <c r="C163" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D163" t="s">
+        <v>424</v>
+      </c>
+      <c r="E163" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>163</v>
       </c>
@@ -2980,8 +4726,14 @@
       <c r="C164" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D164" t="s">
+        <v>425</v>
+      </c>
+      <c r="E164" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>164</v>
       </c>
@@ -2991,8 +4743,14 @@
       <c r="C165" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D165" t="s">
+        <v>426</v>
+      </c>
+      <c r="E165" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>165</v>
       </c>
@@ -3002,8 +4760,14 @@
       <c r="C166" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D166" t="s">
+        <v>427</v>
+      </c>
+      <c r="E166" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>166</v>
       </c>
@@ -3013,8 +4777,14 @@
       <c r="C167" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D167" t="s">
+        <v>428</v>
+      </c>
+      <c r="E167" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>167</v>
       </c>
@@ -3024,8 +4794,14 @@
       <c r="C168" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D168" t="s">
+        <v>429</v>
+      </c>
+      <c r="E168" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>168</v>
       </c>
@@ -3035,8 +4811,14 @@
       <c r="C169" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D169" t="s">
+        <v>430</v>
+      </c>
+      <c r="E169" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>169</v>
       </c>
@@ -3046,8 +4828,14 @@
       <c r="C170" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D170" t="s">
+        <v>431</v>
+      </c>
+      <c r="E170" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>170</v>
       </c>
@@ -3057,8 +4845,14 @@
       <c r="C171" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D171" t="s">
+        <v>432</v>
+      </c>
+      <c r="E171" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>171</v>
       </c>
@@ -3068,8 +4862,14 @@
       <c r="C172" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D172" t="s">
+        <v>433</v>
+      </c>
+      <c r="E172" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>172</v>
       </c>
@@ -3079,8 +4879,14 @@
       <c r="C173" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D173" t="s">
+        <v>434</v>
+      </c>
+      <c r="E173" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>173</v>
       </c>
@@ -3090,8 +4896,14 @@
       <c r="C174" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D174" t="s">
+        <v>435</v>
+      </c>
+      <c r="E174" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>174</v>
       </c>
@@ -3101,8 +4913,14 @@
       <c r="C175" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D175" t="s">
+        <v>436</v>
+      </c>
+      <c r="E175" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>175</v>
       </c>
@@ -3112,8 +4930,14 @@
       <c r="C176" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D176" t="s">
+        <v>437</v>
+      </c>
+      <c r="E176" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>176</v>
       </c>
@@ -3123,8 +4947,14 @@
       <c r="C177" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D177" t="s">
+        <v>438</v>
+      </c>
+      <c r="E177" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>177</v>
       </c>
@@ -3134,8 +4964,14 @@
       <c r="C178" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D178" t="s">
+        <v>439</v>
+      </c>
+      <c r="E178" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>178</v>
       </c>
@@ -3145,8 +4981,14 @@
       <c r="C179" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D179" t="s">
+        <v>440</v>
+      </c>
+      <c r="E179" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>179</v>
       </c>
@@ -3156,8 +4998,14 @@
       <c r="C180" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D180" t="s">
+        <v>441</v>
+      </c>
+      <c r="E180" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>180</v>
       </c>
@@ -3167,8 +5015,14 @@
       <c r="C181" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D181" t="s">
+        <v>442</v>
+      </c>
+      <c r="E181" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>181</v>
       </c>
@@ -3178,8 +5032,14 @@
       <c r="C182" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D182" t="s">
+        <v>443</v>
+      </c>
+      <c r="E182" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>182</v>
       </c>
@@ -3189,8 +5049,14 @@
       <c r="C183" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D183" t="s">
+        <v>444</v>
+      </c>
+      <c r="E183" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>183</v>
       </c>
@@ -3200,8 +5066,14 @@
       <c r="C184" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D184" t="s">
+        <v>445</v>
+      </c>
+      <c r="E184" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>184</v>
       </c>
@@ -3211,8 +5083,14 @@
       <c r="C185" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D185" t="s">
+        <v>446</v>
+      </c>
+      <c r="E185" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>185</v>
       </c>
@@ -3222,8 +5100,14 @@
       <c r="C186" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D186" t="s">
+        <v>447</v>
+      </c>
+      <c r="E186" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>186</v>
       </c>
@@ -3233,8 +5117,14 @@
       <c r="C187" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D187" t="s">
+        <v>448</v>
+      </c>
+      <c r="E187" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>187</v>
       </c>
@@ -3244,8 +5134,14 @@
       <c r="C188" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D188" t="s">
+        <v>449</v>
+      </c>
+      <c r="E188" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>188</v>
       </c>
@@ -3255,8 +5151,14 @@
       <c r="C189" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D189" t="s">
+        <v>450</v>
+      </c>
+      <c r="E189" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>189</v>
       </c>
@@ -3266,8 +5168,14 @@
       <c r="C190" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D190" t="s">
+        <v>451</v>
+      </c>
+      <c r="E190" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>190</v>
       </c>
@@ -3277,8 +5185,14 @@
       <c r="C191" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D191" t="s">
+        <v>452</v>
+      </c>
+      <c r="E191" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>191</v>
       </c>
@@ -3288,8 +5202,14 @@
       <c r="C192" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D192" t="s">
+        <v>453</v>
+      </c>
+      <c r="E192" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>192</v>
       </c>
@@ -3299,8 +5219,14 @@
       <c r="C193" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D193" t="s">
+        <v>454</v>
+      </c>
+      <c r="E193" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>193</v>
       </c>
@@ -3310,8 +5236,14 @@
       <c r="C194" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D194" t="s">
+        <v>455</v>
+      </c>
+      <c r="E194" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>194</v>
       </c>
@@ -3321,8 +5253,14 @@
       <c r="C195" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D195" t="s">
+        <v>456</v>
+      </c>
+      <c r="E195" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>195</v>
       </c>
@@ -3332,8 +5270,14 @@
       <c r="C196" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D196" t="s">
+        <v>457</v>
+      </c>
+      <c r="E196" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>196</v>
       </c>
@@ -3343,8 +5287,14 @@
       <c r="C197" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D197" t="s">
+        <v>458</v>
+      </c>
+      <c r="E197" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>197</v>
       </c>
@@ -3354,8 +5304,14 @@
       <c r="C198" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D198" t="s">
+        <v>459</v>
+      </c>
+      <c r="E198" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>198</v>
       </c>
@@ -3365,8 +5321,14 @@
       <c r="C199" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D199" t="s">
+        <v>460</v>
+      </c>
+      <c r="E199" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>199</v>
       </c>
@@ -3376,8 +5338,14 @@
       <c r="C200" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D200" t="s">
+        <v>461</v>
+      </c>
+      <c r="E200" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>200</v>
       </c>
@@ -3387,8 +5355,14 @@
       <c r="C201" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D201" t="s">
+        <v>462</v>
+      </c>
+      <c r="E201" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>201</v>
       </c>
@@ -3398,8 +5372,14 @@
       <c r="C202" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D202" t="s">
+        <v>463</v>
+      </c>
+      <c r="E202" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>202</v>
       </c>
@@ -3409,8 +5389,14 @@
       <c r="C203" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D203" t="s">
+        <v>464</v>
+      </c>
+      <c r="E203" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>203</v>
       </c>
@@ -3420,8 +5406,14 @@
       <c r="C204" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D204" t="s">
+        <v>465</v>
+      </c>
+      <c r="E204" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>204</v>
       </c>
@@ -3431,8 +5423,14 @@
       <c r="C205" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D205" t="s">
+        <v>466</v>
+      </c>
+      <c r="E205" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>205</v>
       </c>
@@ -3442,8 +5440,14 @@
       <c r="C206" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D206" t="s">
+        <v>467</v>
+      </c>
+      <c r="E206" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>206</v>
       </c>
@@ -3453,8 +5457,14 @@
       <c r="C207" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D207" t="s">
+        <v>468</v>
+      </c>
+      <c r="E207" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>207</v>
       </c>
@@ -3464,8 +5474,14 @@
       <c r="C208" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D208" t="s">
+        <v>469</v>
+      </c>
+      <c r="E208" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>208</v>
       </c>
@@ -3475,8 +5491,14 @@
       <c r="C209" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D209" t="s">
+        <v>470</v>
+      </c>
+      <c r="E209" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>209</v>
       </c>
@@ -3486,8 +5508,14 @@
       <c r="C210" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D210" t="s">
+        <v>471</v>
+      </c>
+      <c r="E210" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>210</v>
       </c>
@@ -3497,8 +5525,14 @@
       <c r="C211" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D211" t="s">
+        <v>472</v>
+      </c>
+      <c r="E211" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>211</v>
       </c>
@@ -3508,8 +5542,14 @@
       <c r="C212" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D212" t="s">
+        <v>473</v>
+      </c>
+      <c r="E212" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>212</v>
       </c>
@@ -3519,8 +5559,14 @@
       <c r="C213" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D213" t="s">
+        <v>474</v>
+      </c>
+      <c r="E213" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>213</v>
       </c>
@@ -3530,8 +5576,14 @@
       <c r="C214" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D214" t="s">
+        <v>475</v>
+      </c>
+      <c r="E214" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>214</v>
       </c>
@@ -3541,8 +5593,14 @@
       <c r="C215" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D215" t="s">
+        <v>476</v>
+      </c>
+      <c r="E215" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>215</v>
       </c>
@@ -3552,8 +5610,14 @@
       <c r="C216" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D216" t="s">
+        <v>477</v>
+      </c>
+      <c r="E216" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>216</v>
       </c>
@@ -3563,8 +5627,14 @@
       <c r="C217" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D217" t="s">
+        <v>478</v>
+      </c>
+      <c r="E217" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>217</v>
       </c>
@@ -3574,8 +5644,14 @@
       <c r="C218" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D218" t="s">
+        <v>479</v>
+      </c>
+      <c r="E218" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>218</v>
       </c>
@@ -3585,8 +5661,14 @@
       <c r="C219" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D219" t="s">
+        <v>480</v>
+      </c>
+      <c r="E219" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>219</v>
       </c>
@@ -3596,8 +5678,14 @@
       <c r="C220" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D220" t="s">
+        <v>481</v>
+      </c>
+      <c r="E220" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>220</v>
       </c>
@@ -3607,8 +5695,14 @@
       <c r="C221" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D221" t="s">
+        <v>482</v>
+      </c>
+      <c r="E221" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>221</v>
       </c>
@@ -3618,8 +5712,14 @@
       <c r="C222" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D222" t="s">
+        <v>483</v>
+      </c>
+      <c r="E222" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>222</v>
       </c>
@@ -3629,8 +5729,14 @@
       <c r="C223" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D223" t="s">
+        <v>484</v>
+      </c>
+      <c r="E223" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>223</v>
       </c>
@@ -3640,8 +5746,14 @@
       <c r="C224" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D224" t="s">
+        <v>485</v>
+      </c>
+      <c r="E224" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>224</v>
       </c>
@@ -3651,8 +5763,14 @@
       <c r="C225" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D225" t="s">
+        <v>486</v>
+      </c>
+      <c r="E225" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>225</v>
       </c>
@@ -3662,8 +5780,14 @@
       <c r="C226" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D226" t="s">
+        <v>487</v>
+      </c>
+      <c r="E226" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <v>226</v>
       </c>
@@ -3673,8 +5797,14 @@
       <c r="C227" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D227" t="s">
+        <v>488</v>
+      </c>
+      <c r="E227" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>227</v>
       </c>
@@ -3684,8 +5814,14 @@
       <c r="C228" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D228" t="s">
+        <v>489</v>
+      </c>
+      <c r="E228" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>228</v>
       </c>
@@ -3695,8 +5831,14 @@
       <c r="C229" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D229" t="s">
+        <v>490</v>
+      </c>
+      <c r="E229" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>229</v>
       </c>
@@ -3706,8 +5848,14 @@
       <c r="C230" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D230" t="s">
+        <v>491</v>
+      </c>
+      <c r="E230" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>230</v>
       </c>
@@ -3717,8 +5865,14 @@
       <c r="C231" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D231" t="s">
+        <v>492</v>
+      </c>
+      <c r="E231" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>231</v>
       </c>
@@ -3728,8 +5882,14 @@
       <c r="C232" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D232" t="s">
+        <v>493</v>
+      </c>
+      <c r="E232" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>232</v>
       </c>
@@ -3739,8 +5899,14 @@
       <c r="C233" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D233" t="s">
+        <v>494</v>
+      </c>
+      <c r="E233" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>233</v>
       </c>
@@ -3750,8 +5916,14 @@
       <c r="C234" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D234" t="s">
+        <v>495</v>
+      </c>
+      <c r="E234" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <v>234</v>
       </c>
@@ -3761,8 +5933,14 @@
       <c r="C235" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D235" t="s">
+        <v>496</v>
+      </c>
+      <c r="E235" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <v>235</v>
       </c>
@@ -3772,8 +5950,14 @@
       <c r="C236" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D236" t="s">
+        <v>497</v>
+      </c>
+      <c r="E236" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <v>236</v>
       </c>
@@ -3783,8 +5967,14 @@
       <c r="C237" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D237" t="s">
+        <v>498</v>
+      </c>
+      <c r="E237" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <v>237</v>
       </c>
@@ -3794,8 +5984,14 @@
       <c r="C238" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D238" t="s">
+        <v>499</v>
+      </c>
+      <c r="E238" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <v>238</v>
       </c>
@@ -3805,8 +6001,14 @@
       <c r="C239" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D239" t="s">
+        <v>500</v>
+      </c>
+      <c r="E239" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <v>239</v>
       </c>
@@ -3816,8 +6018,14 @@
       <c r="C240" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D240" t="s">
+        <v>501</v>
+      </c>
+      <c r="E240" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <v>240</v>
       </c>
@@ -3827,8 +6035,14 @@
       <c r="C241" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D241" t="s">
+        <v>502</v>
+      </c>
+      <c r="E241" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
         <v>241</v>
       </c>
@@ -3838,8 +6052,14 @@
       <c r="C242" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D242" t="s">
+        <v>503</v>
+      </c>
+      <c r="E242" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <v>242</v>
       </c>
@@ -3849,8 +6069,14 @@
       <c r="C243" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D243" t="s">
+        <v>504</v>
+      </c>
+      <c r="E243" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <v>243</v>
       </c>
@@ -3860,8 +6086,14 @@
       <c r="C244" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D244" t="s">
+        <v>505</v>
+      </c>
+      <c r="E244" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
         <v>244</v>
       </c>
@@ -3871,8 +6103,14 @@
       <c r="C245" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D245" t="s">
+        <v>506</v>
+      </c>
+      <c r="E245" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
         <v>245</v>
       </c>
@@ -3882,8 +6120,14 @@
       <c r="C246" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D246" t="s">
+        <v>507</v>
+      </c>
+      <c r="E246" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <v>246</v>
       </c>
@@ -3893,8 +6137,14 @@
       <c r="C247" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D247" t="s">
+        <v>508</v>
+      </c>
+      <c r="E247" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <v>247</v>
       </c>
@@ -3904,8 +6154,14 @@
       <c r="C248" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D248" t="s">
+        <v>509</v>
+      </c>
+      <c r="E248" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <v>248</v>
       </c>
@@ -3915,8 +6171,14 @@
       <c r="C249" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D249" t="s">
+        <v>510</v>
+      </c>
+      <c r="E249" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <v>249</v>
       </c>
@@ -3926,8 +6188,14 @@
       <c r="C250" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D250" t="s">
+        <v>511</v>
+      </c>
+      <c r="E250" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <v>250</v>
       </c>
@@ -3937,8 +6205,14 @@
       <c r="C251" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D251" t="s">
+        <v>512</v>
+      </c>
+      <c r="E251" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
         <v>251</v>
       </c>
@@ -3948,8 +6222,14 @@
       <c r="C252" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D252" t="s">
+        <v>513</v>
+      </c>
+      <c r="E252" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <v>252</v>
       </c>
@@ -3959,8 +6239,14 @@
       <c r="C253" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D253" t="s">
+        <v>514</v>
+      </c>
+      <c r="E253" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <v>253</v>
       </c>
@@ -3970,8 +6256,14 @@
       <c r="C254" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D254" t="s">
+        <v>515</v>
+      </c>
+      <c r="E254" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
         <v>254</v>
       </c>
@@ -3981,8 +6273,14 @@
       <c r="C255" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D255" t="s">
+        <v>516</v>
+      </c>
+      <c r="E255" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
         <v>255</v>
       </c>
@@ -3992,8 +6290,14 @@
       <c r="C256" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D256" t="s">
+        <v>517</v>
+      </c>
+      <c r="E256" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
         <v>256</v>
       </c>
@@ -4002,6 +6306,12 @@
       </c>
       <c r="C257" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="D257" t="s">
+        <v>518</v>
+      </c>
+      <c r="E257" s="1">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
